--- a/Excel/Weapon.xlsx
+++ b/Excel/Weapon.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -32,7 +32,10 @@
     <t xml:space="preserve">ResourceID</t>
   </si>
   <si>
-    <t xml:space="preserve">BoneName</t>
+    <t xml:space="preserve">WeaponBoneName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CharacterBoneName</t>
   </si>
   <si>
     <t xml:space="preserve">ComboIDs</t>
@@ -42,6 +45,12 @@
   </si>
   <si>
     <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand_r_weapon</t>
   </si>
   <si>
     <t xml:space="preserve">Player desc</t>
@@ -155,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -173,6 +182,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -369,15 +382,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="61.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="36.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="8.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="8.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="36.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="8.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="8.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -399,40 +414,51 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
@@ -440,9 +466,10 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
@@ -453,6 +480,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
@@ -463,6 +491,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
@@ -473,6 +502,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
@@ -483,6 +513,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
@@ -493,6 +524,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
@@ -503,6 +535,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
@@ -513,6 +546,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
@@ -523,6 +557,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
@@ -533,6 +568,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
@@ -543,6 +579,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
@@ -553,6 +590,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
@@ -563,6 +601,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
@@ -573,6 +612,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -580,7 +620,7 @@
       <formula1>Enums!$A$1:$A$100</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:E2 C3:E17" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:F2 C3:F17" type="none">
       <formula1>Enums!$A$1:$A$100</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -607,8 +647,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>6</v>
+      <c r="A1" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -616,8 +656,8 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
+      <c r="A2" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>

--- a/Excel/Weapon.xlsx
+++ b/Excel/Weapon.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">Type</t>
+    <t xml:space="preserve">eType</t>
   </si>
   <si>
     <t xml:space="preserve">ResourceID</t>
@@ -389,7 +389,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="36.7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="8.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="8.12"/>

--- a/Excel/Weapon.xlsx
+++ b/Excel/Weapon.xlsx
@@ -436,7 +436,9 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
